--- a/inspection_forms/036_fire_alarm_inspection_checklist_form--inspection_forms.xlsx
+++ b/inspection_forms/036_fire_alarm_inspection_checklist_form--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,46 +515,54 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fire_alarm_inspection_checklist_form_page_1</t>
+          <t>fire_alarm_inspection_status</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fire Alarm Inspection Checklist Form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Check Fire Alarm Connection Status</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Check if the fire alarm connection is working or not working</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>general_information</t>
+          <t>fire_alarm_sensors_status</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>General Information</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Check Fire Alarm Sensors Status</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Inspect the status of fire alarm sensors</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fire_alarm_connection_status</t>
+          <t>fire_alarm_controllers_status</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fire Alarm Connection Status</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Check Fire Alarm Controllers Status</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Inspect the status of fire alarm controllers</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fire_alarm_sensors_status</t>
+          <t>fire_alarm_panels_status</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fire Alarm Sensors Status</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Check Fire Alarm Panels Status</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Inspect the status of fire alarm panels</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -612,15 +628,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fire_alarm_controllers_status</t>
+          <t>fire_alarm_controllers_panel_connection_status</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fire Alarm Controllers Status</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Check Fire Alarm Controllers and Panels Connection Status</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Inspect the connection status of fire alarm controllers and panels</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>yes</t>
@@ -630,20 +650,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fire_alarm_panels_status</t>
+          <t>fire_alarm_wiring_status</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fire Alarm Panels Status</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Check Fire Alarm Wiring Status</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Inspect the status of fire alarm wiring</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fire_alarm_controllers_panel_connection_status</t>
+          <t>fire_alarm_maintenance_status</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fire Alarm Controllers Panel Connection Status</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Check Fire Alarm Maintenance Status</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Check the fire alarm maintenance status</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>yes</t>
@@ -676,20 +704,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fire_alarm_wiring_status</t>
+          <t>fire_alarm_testing_status</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fire Alarm Wiring</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Check Fire Alarm Testing Status</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Check the fire alarm testing status</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fire_alarm_maintenance_status</t>
+          <t>fire_alarm_standards_compliance_status</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fire Alarm Maintenance Status</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Check Fire Alarm Standards Compliance Status</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Check the fire alarm standards compliance status</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fire_alarm_testing_status</t>
+          <t>fire_alarm_inspection_frequency</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fire Alarm Testing Status</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Check Fire Alarm Inspection Frequency</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Check the fire alarm system inspection frequency</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -745,20 +785,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fire_alarm_standards_compliance_status</t>
+          <t>fire_alarm_system_inspection_last_date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fire Alarm Standards Compliance Status</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Check Fire Alarm System Last Inspection Date</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Check the last fire alarm system inspection date</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -768,20 +812,24 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fire_alarm_system_inspection_frequency</t>
+          <t>fire_alarm_system_inspection_next_date</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fire Alarm System Inspection Frequency</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Check Fire Alarm System Next Inspection Date</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Check the next fire alarm system inspection date</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>yes</t>
@@ -791,20 +839,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>fire_alarm_system_inspection_last_date</t>
+          <t>fire_alarm_system_inspection_duration</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fire Alarm System Last Inspection Date</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Check Fire Alarm System Inspection Duration</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Check the fire alarm system inspection duration</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>yes</t>
@@ -814,20 +866,24 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>fire_alarm_system_inspection_next_date</t>
+          <t>fire_alarm_system_inspection_remark</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fire Alarm System Next Inspection Date</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Fire Alarm System Inspection Remark</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Enter any remark about the inspection</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>yes</t>
@@ -837,20 +893,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>fire_alarm_system_inspection_duration</t>
+          <t>fire_alarm_system_inspection_signature</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fire Alarm System Inspection Duration</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Fire Alarm System Inspection Signature</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Enter your name as the inspector</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>yes</t>
@@ -860,20 +920,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fire_alarm_system_inspection_remark</t>
+          <t>fire_alarm_system_inspection_signature_date</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fire Alarm System Inspection Remark</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Fire Alarm System Inspection Signature Date</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Enter the signature date</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>yes</t>
@@ -883,205 +947,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>fire_alarm_system_inspection_signature</t>
+          <t>fire_alarm_system_inspection_signature_time</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fire Alarm System Inspection Signature</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Fire Alarm System Inspection Signature Time</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Enter the signature time</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>fire_alarm_system_inspection_signature_date</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Fire Alarm System Inspection Signature Date</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>fire_alarm_system_inspection_signature_time</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Fire Alarm System Inspection Signature Time</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>fire_alarm_system_inspection_signature</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Fire Alarm System Inspection Signature</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>fire_alarm_system_inspection_signature_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Fire Alarm System Inspection Signature</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>fire_alarm_system_inspection_signature_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Fire Alarm System Inspection Signature</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>fire_alarm_system_inspection_signature_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Fire Alarm System Inspection Signature</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>fire_alarm_system_inspection_signature_5</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Fire Alarm System Inspection Signature</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>fire_alarm_system_inspection_signature_6</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Fire Alarm System Inspection Signature</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1102,8 +986,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,34 +1010,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fire_alarm_connection_status_choices</t>
+          <t>fire_alarm_inspection_status_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>connection_is_working</t>
+          <t>working</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Connection is working</t>
+          <t>Working</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fire_alarm_connection_status_choices</t>
+          <t>fire_alarm_inspection_status_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>connection_is_not_working</t>
+          <t>not_working</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Connection is not working</t>
+          <t>Not Working</t>
         </is>
       </c>
     </row>
@@ -1568,7 +1452,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fire_alarm_system_inspection_frequency_choices</t>
+          <t>fire_alarm_inspection_frequency_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1469,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>fire_alarm_system_inspection_frequency_choices</t>
+          <t>fire_alarm_inspection_frequency_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,7 +1486,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>fire_alarm_system_inspection_frequency_choices</t>
+          <t>fire_alarm_inspection_frequency_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
